--- a/DRAGO/Julio/EXPENSAS-Julio.xlsx
+++ b/DRAGO/Julio/EXPENSAS-Julio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\DRAGO\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A079FB6A-8060-451B-B8C1-6A1CFDF2F111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D245DC-F154-4AAF-A7AE-A3330118218D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -298,13 +298,13 @@
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t>LIQUIDACIÓN EXPENSAS julio 2025</t>
-  </si>
-  <si>
     <t>Período julio 2025</t>
   </si>
   <si>
     <t>Vto. 14/08</t>
+  </si>
+  <si>
+    <t>LIQUIDACIÓN EXPENSAS JULIO 2025</t>
   </si>
 </sst>
 </file>
@@ -312,11 +312,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -867,9 +867,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -880,7 +880,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -903,14 +903,14 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -928,7 +928,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -936,10 +936,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -948,13 +948,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -962,11 +962,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -976,7 +976,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -999,7 +999,7 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1007,7 +1007,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1017,15 +1017,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1040,9 +1039,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1050,8 +1049,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1103,10 +1102,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1477,16 +1476,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -1494,43 +1493,43 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1538,7 +1537,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1546,37 +1545,37 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="86" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="77"/>
-      <c r="C16" s="11"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="119"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="77" t="s">
         <v>54</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="99">
+      <c r="C17" s="84">
         <v>41718</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="14"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="77" t="s">
         <v>71</v>
       </c>
@@ -1587,34 +1586,34 @@
       <c r="D18" s="49"/>
       <c r="E18" s="14"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="77" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="99">
+      <c r="C19" s="84">
         <v>15030.94</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="14"/>
       <c r="F19" s="18"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="77" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="138">
+      <c r="C20" s="137">
         <v>145207.69</v>
       </c>
       <c r="D20" s="49"/>
       <c r="F20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>36</v>
       </c>
@@ -1630,7 +1629,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="90"/>
       <c r="B22" s="91"/>
       <c r="C22" s="64">
@@ -1638,19 +1637,19 @@
         <v>250023.84</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="86" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="89"/>
-      <c r="C23" s="120"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C23" s="119"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="77" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="92" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C24" s="84">
         <f>65200+65200*5%</f>
@@ -1658,17 +1657,17 @@
       </c>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="77" t="s">
         <v>89</v>
       </c>
       <c r="B25" s="92"/>
-      <c r="C25" s="99">
+      <c r="C25" s="84">
         <v>33650</v>
       </c>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="77" t="s">
         <v>83</v>
       </c>
@@ -1678,7 +1677,7 @@
       <c r="E26" s="14"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="64">
@@ -1687,7 +1686,7 @@
       </c>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="80" t="s">
         <v>82</v>
       </c>
@@ -1698,40 +1697,40 @@
       </c>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C29" s="65"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="65"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="77"/>
       <c r="B31" s="77"/>
       <c r="C31" s="84"/>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="77"/>
       <c r="B32" s="77"/>
       <c r="C32" s="85"/>
       <c r="F32" s="22"/>
     </row>
-    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="77"/>
       <c r="B33" s="77"/>
       <c r="C33" s="85"/>
       <c r="F33" s="22"/>
     </row>
-    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C34" s="67"/>
       <c r="F34" s="22"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
         <v>43</v>
       </c>
@@ -1742,7 +1741,7 @@
       </c>
       <c r="E35" s="14"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="35" t="s">
         <v>15</v>
       </c>
@@ -1752,34 +1751,34 @@
         <v>352133.83999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
         <v>10</v>
       </c>
       <c r="B40" s="34"/>
       <c r="C40" s="41">
-        <v>260801.88812239992</v>
+        <v>330849.82114340004</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="33">
         <f>'prorrateo '!F13</f>
-        <v>391672.39302100008</v>
+        <v>353941.62798998912</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -1787,7 +1786,7 @@
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>79</v>
       </c>
@@ -1796,48 +1795,48 @@
         <v>-352133.83999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="37" t="s">
         <v>16</v>
       </c>
       <c r="B44" s="34"/>
       <c r="C44" s="41">
         <f>SUM(C40:C43)</f>
-        <v>300340.44114340004</v>
+        <v>332657.6091333892</v>
       </c>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="19"/>
       <c r="B45" s="18"/>
       <c r="C45" s="20"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="19"/>
       <c r="B46" s="18"/>
       <c r="C46" s="20"/>
       <c r="F46" s="95"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="19"/>
       <c r="B47" s="18"/>
       <c r="C47" s="20"/>
     </row>
-    <row r="48" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="B48" s="100"/>
-      <c r="C48" s="101">
+      <c r="B48" s="99"/>
+      <c r="C48" s="100">
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="77"/>
       <c r="B49" s="77"/>
       <c r="C49" s="83"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="80" t="s">
         <v>4</v>
       </c>
@@ -1847,22 +1846,22 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="18"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="18"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="18"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="18"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
@@ -1884,111 +1883,111 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.44140625" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="55" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="51">
-        <v>321624.45999999996</v>
+        <v>352133.83999999997</v>
       </c>
       <c r="G1" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 14/08</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="107" t="str">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="106" t="str">
         <f>'detalle y gastos'!B7</f>
-        <v>LIQUIDACIÓN EXPENSAS julio 2025</v>
-      </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="109" t="s">
+        <v>LIQUIDACIÓN EXPENSAS JULIO 2025</v>
+      </c>
+      <c r="B2" s="101"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="103"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="124"/>
-      <c r="B3" s="122" t="s">
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="102"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="123"/>
+      <c r="B3" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="C3" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="131" t="s">
+      <c r="D3" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="122" t="s">
+      <c r="E3" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="128" t="s">
+      <c r="F3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="130" t="s">
+      <c r="G3" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="128" t="s">
+      <c r="H3" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="130" t="s">
+      <c r="I3" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="132" t="s">
+      <c r="J3" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="126" t="s">
+      <c r="K3" s="125" t="s">
         <v>84</v>
       </c>
-      <c r="L3" s="126" t="s">
+      <c r="L3" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="M3" s="126" t="s">
+      <c r="M3" s="125" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="125"/>
-      <c r="B4" s="123"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="123"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="127"/>
-      <c r="L4" s="127"/>
-      <c r="M4" s="127"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="104">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="124"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="103">
         <v>1</v>
       </c>
       <c r="B5" s="12" t="s">
@@ -2001,11 +2000,11 @@
         <v>66</v>
       </c>
       <c r="E5" s="47">
-        <v>38532.256399999998</v>
-      </c>
-      <c r="F5" s="121">
+        <v>38916.559659999992</v>
+      </c>
+      <c r="F5" s="120">
         <f>E5</f>
-        <v>38532.256399999998</v>
+        <v>38916.559659999992</v>
       </c>
       <c r="G5" s="47">
         <f>E5-F5</f>
@@ -2015,25 +2014,25 @@
         <f>IF(G5&gt;0,G5*5%,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="110">
+      <c r="I5" s="109">
         <v>0.121</v>
       </c>
       <c r="J5" s="98"/>
-      <c r="K5" s="111">
+      <c r="K5" s="110">
         <f>E1*I5</f>
-        <v>38916.559659999992</v>
-      </c>
-      <c r="L5" s="111">
+        <v>42608.194639999994</v>
+      </c>
+      <c r="L5" s="110">
         <f>E5-F5+H5+K5+J5</f>
-        <v>38916.559659999992</v>
-      </c>
-      <c r="M5" s="112">
+        <v>42608.194639999994</v>
+      </c>
+      <c r="M5" s="111">
         <f>L5+L5*4%</f>
-        <v>40473.222046399991</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="104">
+        <v>44312.522425599993</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="103">
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -2046,11 +2045,11 @@
         <v>67</v>
       </c>
       <c r="E6" s="47">
-        <v>47715.447421000004</v>
-      </c>
-      <c r="F6" s="121">
+        <v>39238.184119999998</v>
+      </c>
+      <c r="F6" s="120">
         <f>E6</f>
-        <v>47715.447421000004</v>
+        <v>39238.184119999998</v>
       </c>
       <c r="G6" s="47">
         <f t="shared" ref="G6:G12" si="0">E6-F6</f>
@@ -2060,27 +2059,27 @@
         <f t="shared" ref="H6:H12" si="1">IF(G6&gt;0,G6*5%,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="110">
+      <c r="I6" s="109">
         <v>0.122</v>
       </c>
       <c r="J6" s="98"/>
-      <c r="K6" s="111">
+      <c r="K6" s="110">
         <f>E1*I6</f>
-        <v>39238.184119999998</v>
-      </c>
-      <c r="L6" s="111">
+        <v>42960.328479999996</v>
+      </c>
+      <c r="L6" s="110">
         <f t="shared" ref="L6:L12" si="2">E6-F6+H6+K6+J6</f>
-        <v>39238.184119999998</v>
-      </c>
-      <c r="M6" s="112">
+        <v>42960.328479999996</v>
+      </c>
+      <c r="M6" s="111">
         <f t="shared" ref="M6:M12" si="3">L6+L6*4%</f>
-        <v>40807.711484799998</v>
-      </c>
-      <c r="O6" s="119"/>
-      <c r="Q6" s="118"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="104">
+        <v>44678.741619199995</v>
+      </c>
+      <c r="O6" s="118"/>
+      <c r="Q6" s="117"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="103">
         <v>3</v>
       </c>
       <c r="B7" s="12" t="s">
@@ -2093,39 +2092,36 @@
         <v>87</v>
       </c>
       <c r="E7" s="47">
-        <v>37258.462800000008</v>
-      </c>
-      <c r="F7" s="121">
-        <f>E7</f>
-        <v>37258.462800000008</v>
-      </c>
+        <v>37630.061819999995</v>
+      </c>
+      <c r="F7" s="120"/>
       <c r="G7" s="47">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>37630.061819999995</v>
       </c>
       <c r="H7" s="47">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="110">
+        <v>1881.5030909999998</v>
+      </c>
+      <c r="I7" s="109">
         <v>0.11700000000000001</v>
       </c>
       <c r="J7" s="98"/>
-      <c r="K7" s="111">
+      <c r="K7" s="110">
         <f>E1*I7</f>
-        <v>37630.061819999995</v>
-      </c>
-      <c r="L7" s="111">
+        <v>41199.65928</v>
+      </c>
+      <c r="L7" s="110">
         <f t="shared" si="2"/>
-        <v>37630.061819999995</v>
-      </c>
-      <c r="M7" s="112">
+        <v>80711.224190999987</v>
+      </c>
+      <c r="M7" s="111">
         <f t="shared" si="3"/>
-        <v>39135.264292799999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="104">
+        <v>83939.673158639984</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="103">
         <v>4</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -2138,38 +2134,39 @@
         <v>62</v>
       </c>
       <c r="E8" s="47">
-        <v>165459.88212379918</v>
-      </c>
-      <c r="F8" s="121">
-        <v>100000</v>
+        <v>106362.93804998914</v>
+      </c>
+      <c r="F8" s="120">
+        <f>E8</f>
+        <v>106362.93804998914</v>
       </c>
       <c r="G8" s="47">
         <f t="shared" si="0"/>
-        <v>65459.88212379918</v>
+        <v>0</v>
       </c>
       <c r="H8" s="47">
         <f t="shared" si="1"/>
-        <v>3272.994106189959</v>
-      </c>
-      <c r="I8" s="110">
+        <v>0</v>
+      </c>
+      <c r="I8" s="109">
         <v>0.11700000000000001</v>
       </c>
       <c r="J8" s="98"/>
-      <c r="K8" s="111">
+      <c r="K8" s="110">
         <f>E1*I8</f>
-        <v>37630.061819999995</v>
-      </c>
-      <c r="L8" s="111">
+        <v>41199.65928</v>
+      </c>
+      <c r="L8" s="110">
         <f t="shared" si="2"/>
-        <v>106362.93804998914</v>
-      </c>
-      <c r="M8" s="112">
+        <v>41199.65928</v>
+      </c>
+      <c r="M8" s="111">
         <f t="shared" si="3"/>
-        <v>110617.45557198871</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="104">
+        <v>42847.6456512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="103">
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
@@ -2182,11 +2179,11 @@
         <v>65</v>
       </c>
       <c r="E9" s="47">
-        <v>43627.430800000009</v>
-      </c>
-      <c r="F9" s="121">
-        <f t="shared" ref="F9" si="4">E9</f>
-        <v>43627.430800000009</v>
+        <v>44062.551019999999</v>
+      </c>
+      <c r="F9" s="120">
+        <f>E9</f>
+        <v>44062.551019999999</v>
       </c>
       <c r="G9" s="47">
         <f t="shared" si="0"/>
@@ -2196,25 +2193,25 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I9" s="110">
+      <c r="I9" s="109">
         <v>0.13700000000000001</v>
       </c>
       <c r="J9" s="98"/>
-      <c r="K9" s="111">
+      <c r="K9" s="110">
         <f>E1*I9</f>
-        <v>44062.551019999999</v>
-      </c>
-      <c r="L9" s="111">
+        <v>48242.336080000001</v>
+      </c>
+      <c r="L9" s="110">
         <f t="shared" si="2"/>
-        <v>44062.551019999999</v>
-      </c>
-      <c r="M9" s="112">
+        <v>48242.336080000001</v>
+      </c>
+      <c r="M9" s="111">
         <f t="shared" si="3"/>
-        <v>45825.053060799997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="104">
+        <v>50172.029523199999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="103">
         <v>6</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -2227,11 +2224,11 @@
         <v>64</v>
       </c>
       <c r="E10" s="47">
-        <v>42035.188800000004</v>
-      </c>
-      <c r="F10" s="121">
+        <v>42454.428719999996</v>
+      </c>
+      <c r="F10" s="120">
         <f>E10</f>
-        <v>42035.188800000004</v>
+        <v>42454.428719999996</v>
       </c>
       <c r="G10" s="47">
         <f t="shared" si="0"/>
@@ -2241,25 +2238,25 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I10" s="110">
+      <c r="I10" s="109">
         <v>0.13200000000000001</v>
       </c>
       <c r="J10" s="98"/>
-      <c r="K10" s="111">
+      <c r="K10" s="110">
         <f>E1*I10</f>
-        <v>42454.428719999996</v>
-      </c>
-      <c r="L10" s="111">
+        <v>46481.666879999997</v>
+      </c>
+      <c r="L10" s="110">
         <f t="shared" si="2"/>
-        <v>42454.428719999996</v>
-      </c>
-      <c r="M10" s="112">
+        <v>46481.666879999997</v>
+      </c>
+      <c r="M10" s="111">
         <f t="shared" si="3"/>
-        <v>44152.605868799998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="104">
+        <v>48340.933555199997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="103">
         <v>7</v>
       </c>
       <c r="B11" s="12" t="s">
@@ -2272,11 +2269,11 @@
         <v>63</v>
       </c>
       <c r="E11" s="47">
-        <v>40442.946800000005</v>
-      </c>
-      <c r="F11" s="121">
+        <v>40846.306419999994</v>
+      </c>
+      <c r="F11" s="120">
         <f>E11</f>
-        <v>40442.946800000005</v>
+        <v>40846.306419999994</v>
       </c>
       <c r="G11" s="47">
         <f t="shared" si="0"/>
@@ -2286,25 +2283,25 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I11" s="110">
+      <c r="I11" s="109">
         <v>0.127</v>
       </c>
       <c r="J11" s="98"/>
-      <c r="K11" s="111">
+      <c r="K11" s="110">
         <f>E1*I11</f>
-        <v>40846.306419999994</v>
-      </c>
-      <c r="L11" s="111">
+        <v>44720.997679999993</v>
+      </c>
+      <c r="L11" s="110">
         <f t="shared" si="2"/>
-        <v>40846.306419999994</v>
-      </c>
-      <c r="M11" s="112">
+        <v>44720.997679999993</v>
+      </c>
+      <c r="M11" s="111">
         <f t="shared" si="3"/>
-        <v>42480.158676799991</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="104">
+        <v>46509.837587199996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="103">
         <v>8</v>
       </c>
       <c r="B12" s="12" t="s">
@@ -2317,78 +2314,78 @@
         <v>61</v>
       </c>
       <c r="E12" s="47">
-        <v>40442.946800000005</v>
-      </c>
-      <c r="F12" s="121">
+        <v>39228.593219999995</v>
+      </c>
+      <c r="F12" s="120">
         <v>42060.66</v>
       </c>
       <c r="G12" s="47">
         <f t="shared" si="0"/>
-        <v>-1617.7131999999983</v>
+        <v>-2832.0667800000083</v>
       </c>
       <c r="H12" s="47">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I12" s="110">
+      <c r="I12" s="109">
         <v>0.127</v>
       </c>
       <c r="J12" s="98"/>
-      <c r="K12" s="111">
+      <c r="K12" s="110">
         <f>E1*I12</f>
-        <v>40846.306419999994</v>
-      </c>
-      <c r="L12" s="111">
+        <v>44720.997679999993</v>
+      </c>
+      <c r="L12" s="110">
         <f t="shared" si="2"/>
-        <v>39228.593219999995</v>
-      </c>
-      <c r="M12" s="112">
+        <v>41888.930899999985</v>
+      </c>
+      <c r="M12" s="111">
         <f t="shared" si="3"/>
-        <v>40797.736948799997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="113" t="s">
+        <v>43564.488135999985</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="114"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="116">
+      <c r="B13" s="113"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115">
         <f>SUM(E5:E12)</f>
-        <v>455514.56194479926</v>
-      </c>
-      <c r="F13" s="105">
+        <v>388739.62302998907</v>
+      </c>
+      <c r="F13" s="104">
         <f>SUM(F5:F12)</f>
-        <v>391672.39302100008</v>
-      </c>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105">
+        <v>353941.62798998912</v>
+      </c>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104">
         <f>SUM(H5:H12)</f>
-        <v>3272.994106189959</v>
-      </c>
-      <c r="I13" s="106">
-        <f t="shared" ref="I13" si="5">SUM(I5:I12)</f>
+        <v>1881.5030909999998</v>
+      </c>
+      <c r="I13" s="105">
+        <f t="shared" ref="I13" si="4">SUM(I5:I12)</f>
         <v>1</v>
       </c>
-      <c r="J13" s="106">
+      <c r="J13" s="105">
         <f>SUM(J5:J12)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="116">
+      <c r="K13" s="115">
         <f>SUM(K5:K12)</f>
-        <v>321624.45999999996</v>
-      </c>
-      <c r="L13" s="116">
+        <v>352133.83999999991</v>
+      </c>
+      <c r="L13" s="115">
         <f>SUM(L5:L12)</f>
-        <v>388739.62302998907</v>
-      </c>
-      <c r="M13" s="117">
+        <v>388813.33813099994</v>
+      </c>
+      <c r="M13" s="116">
         <f>SUM(M5:M12)</f>
-        <v>404289.20795118867</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+        <v>404365.87165623996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
         <v>53</v>
       </c>
@@ -2396,7 +2393,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
         <v>56</v>
       </c>
@@ -2415,7 +2412,7 @@
       <c r="L17" s="56"/>
       <c r="M17" s="32"/>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
@@ -2448,7 +2445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2475,7 +2472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>1</v>
       </c>
@@ -2510,7 +2507,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>2</v>
       </c>
@@ -2536,7 +2533,7 @@
       </c>
       <c r="J21" s="96"/>
       <c r="K21" s="45">
-        <f t="shared" ref="K21:K27" si="6">0*I21</f>
+        <f t="shared" ref="K21:K27" si="5">0*I21</f>
         <v>0</v>
       </c>
       <c r="L21" s="42"/>
@@ -2545,7 +2542,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>3</v>
       </c>
@@ -2572,7 +2569,7 @@
       </c>
       <c r="J22" s="96"/>
       <c r="K22" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L22" s="42"/>
@@ -2581,7 +2578,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>4</v>
       </c>
@@ -2604,7 +2601,7 @@
       </c>
       <c r="J23" s="96"/>
       <c r="K23" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L23" s="42"/>
@@ -2613,7 +2610,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>5</v>
       </c>
@@ -2636,7 +2633,7 @@
       </c>
       <c r="J24" s="96"/>
       <c r="K24" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L24" s="42"/>
@@ -2645,7 +2642,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>6</v>
       </c>
@@ -2668,7 +2665,7 @@
       </c>
       <c r="J25" s="96"/>
       <c r="K25" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L25" s="42"/>
@@ -2677,7 +2674,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>7</v>
       </c>
@@ -2703,7 +2700,7 @@
       </c>
       <c r="J26" s="96"/>
       <c r="K26" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L26" s="42"/>
@@ -2712,7 +2709,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>8</v>
       </c>
@@ -2738,7 +2735,7 @@
       </c>
       <c r="J27" s="96"/>
       <c r="K27" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L27" s="42"/>
@@ -2747,7 +2744,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>11</v>
       </c>
@@ -2767,12 +2764,12 @@
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" ref="I28:K28" si="7">SUM(I20:I27)</f>
+        <f t="shared" ref="I28:K28" si="6">SUM(I20:I27)</f>
         <v>1</v>
       </c>
       <c r="J28" s="97"/>
       <c r="K28" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L28" s="43"/>
@@ -2781,15 +2778,15 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I30" s="60"/>
       <c r="J30" s="60"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="I31" s="60"/>
       <c r="J31" s="60"/>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E39" s="54"/>
     </row>
   </sheetData>
@@ -2817,39 +2814,39 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D1" s="58">
         <v>50000</v>
       </c>
-      <c r="H1" s="137">
+      <c r="H1" s="136">
         <v>250000</v>
       </c>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
         <v>53</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
         <v>68</v>
       </c>
@@ -2872,7 +2869,7 @@
       <c r="N3" s="32"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2904,18 +2901,18 @@
         <v>58</v>
       </c>
       <c r="K4" s="71"/>
-      <c r="L4" s="135" t="s">
+      <c r="L4" s="134" t="s">
         <v>74</v>
       </c>
       <c r="M4" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="133" t="s">
+      <c r="N4" s="132" t="s">
         <v>59</v>
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2939,14 +2936,14 @@
         <v>73</v>
       </c>
       <c r="K5" s="61"/>
-      <c r="L5" s="136"/>
+      <c r="L5" s="135"/>
       <c r="M5" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="134"/>
+      <c r="N5" s="133"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -2994,7 +2991,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -3042,7 +3039,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -3090,7 +3087,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -3138,7 +3135,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -3186,7 +3183,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -3234,7 +3231,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -3282,7 +3279,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -3330,7 +3327,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>

--- a/DRAGO/Julio/EXPENSAS-Julio.xlsx
+++ b/DRAGO/Julio/EXPENSAS-Julio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D245DC-F154-4AAF-A7AE-A3330118218D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84B3410-E9D7-4E0A-8DD6-238DC6E2563A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -1057,6 +1057,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1104,9 +1107,6 @@
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1607,7 +1607,7 @@
       <c r="B20" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="137">
+      <c r="C20" s="121">
         <v>145207.69</v>
       </c>
       <c r="D20" s="49"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C41" s="33">
         <f>'prorrateo '!F13</f>
-        <v>353941.62798998912</v>
+        <v>391571.68980998907</v>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
@@ -1802,7 +1802,7 @@
       <c r="B44" s="34"/>
       <c r="C44" s="41">
         <f>SUM(C40:C43)</f>
-        <v>332657.6091333892</v>
+        <v>370287.67095338914</v>
       </c>
       <c r="D44" s="6"/>
     </row>
@@ -1933,58 +1933,58 @@
       <c r="M2" s="102"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="123"/>
-      <c r="B3" s="121" t="s">
+      <c r="A3" s="124"/>
+      <c r="B3" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="129" t="s">
+      <c r="C3" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="D3" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="121" t="s">
+      <c r="E3" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="127" t="s">
+      <c r="F3" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="129" t="s">
+      <c r="G3" s="130" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="127" t="s">
+      <c r="H3" s="128" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="129" t="s">
+      <c r="I3" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="131" t="s">
+      <c r="J3" s="132" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="125" t="s">
+      <c r="K3" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="L3" s="125" t="s">
+      <c r="L3" s="126" t="s">
         <v>85</v>
       </c>
-      <c r="M3" s="125" t="s">
+      <c r="M3" s="126" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="124"/>
-      <c r="B4" s="122"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="126"/>
-      <c r="L4" s="126"/>
-      <c r="M4" s="126"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="132"/>
+      <c r="K4" s="127"/>
+      <c r="L4" s="127"/>
+      <c r="M4" s="127"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="103">
@@ -2094,14 +2094,17 @@
       <c r="E7" s="47">
         <v>37630.061819999995</v>
       </c>
-      <c r="F7" s="120"/>
+      <c r="F7" s="120">
+        <f>E7</f>
+        <v>37630.061819999995</v>
+      </c>
       <c r="G7" s="47">
         <f t="shared" si="0"/>
-        <v>37630.061819999995</v>
+        <v>0</v>
       </c>
       <c r="H7" s="47">
         <f t="shared" si="1"/>
-        <v>1881.5030909999998</v>
+        <v>0</v>
       </c>
       <c r="I7" s="109">
         <v>0.11700000000000001</v>
@@ -2113,11 +2116,11 @@
       </c>
       <c r="L7" s="110">
         <f t="shared" si="2"/>
-        <v>80711.224190999987</v>
+        <v>41199.65928</v>
       </c>
       <c r="M7" s="111">
         <f t="shared" si="3"/>
-        <v>83939.673158639984</v>
+        <v>42847.6456512</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -2357,12 +2360,12 @@
       </c>
       <c r="F13" s="104">
         <f>SUM(F5:F12)</f>
-        <v>353941.62798998912</v>
+        <v>391571.68980998907</v>
       </c>
       <c r="G13" s="104"/>
       <c r="H13" s="104">
         <f>SUM(H5:H12)</f>
-        <v>1881.5030909999998</v>
+        <v>0</v>
       </c>
       <c r="I13" s="105">
         <f t="shared" ref="I13" si="4">SUM(I5:I12)</f>
@@ -2378,11 +2381,11 @@
       </c>
       <c r="L13" s="115">
         <f>SUM(L5:L12)</f>
-        <v>388813.33813099994</v>
+        <v>349301.77321999992</v>
       </c>
       <c r="M13" s="116">
         <f>SUM(M5:M12)</f>
-        <v>404365.87165623996</v>
+        <v>363273.84414880001</v>
       </c>
     </row>
     <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
@@ -2833,11 +2836,11 @@
       <c r="D1" s="58">
         <v>50000</v>
       </c>
-      <c r="H1" s="136">
+      <c r="H1" s="137">
         <v>250000</v>
       </c>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
@@ -2901,13 +2904,13 @@
         <v>58</v>
       </c>
       <c r="K4" s="71"/>
-      <c r="L4" s="134" t="s">
+      <c r="L4" s="135" t="s">
         <v>74</v>
       </c>
       <c r="M4" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="132" t="s">
+      <c r="N4" s="133" t="s">
         <v>59</v>
       </c>
       <c r="P4" s="21"/>
@@ -2936,11 +2939,11 @@
         <v>73</v>
       </c>
       <c r="K5" s="61"/>
-      <c r="L5" s="135"/>
+      <c r="L5" s="136"/>
       <c r="M5" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="133"/>
+      <c r="N5" s="134"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
